--- a/resource/table/ko_narration_sets.xlsx
+++ b/resource/table/ko_narration_sets.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\work\LVPD_Studio\resource\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3784650-CC4F-4961-B2E8-BF2EDE5EAF33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{180D5946-2295-46CD-A76C-019AF7807BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-27780" yWindow="3855" windowWidth="32745" windowHeight="15285" xr2:uid="{4ABACD07-DE77-46EA-95A9-D7C0914B6AEB}"/>
+    <workbookView xWindow="-27195" yWindow="14130" windowWidth="32745" windowHeight="15285" xr2:uid="{4ABACD07-DE77-46EA-95A9-D7C0914B6AEB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="14">
   <si>
     <t>id</t>
   </si>
@@ -42,10 +42,43 @@
     <t>title</t>
   </si>
   <si>
-    <t>srt_path</t>
-  </si>
-  <si>
     <t>화장실 어디 ( 예시</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>tts</t>
+  </si>
+  <si>
+    <t>tts_voice</t>
+  </si>
+  <si>
+    <t>edge</t>
+  </si>
+  <si>
+    <t>여</t>
+  </si>
+  <si>
+    <t>선희 (기본값에 가깝게 많이 씀)</t>
+  </si>
+  <si>
+    <t>남</t>
+  </si>
+  <si>
+    <t>인준</t>
+  </si>
+  <si>
+    <t>현수 (다국어 Neural)</t>
+  </si>
+  <si>
+    <t>ko-KR-InJoonNeural</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ko-KR-SunHiNeural</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ko-KR-HyunsuMultilingualNeural</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -53,7 +86,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13">
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -85,13 +118,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFB5CEA8"/>
-      <name val="Consolas"/>
-      <family val="3"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF4EC9B0"/>
       <name val="Consolas"/>
       <family val="3"/>
@@ -144,6 +170,19 @@
       <color rgb="FF57A64A"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF4EC9B0"/>
+      <name val="돋움"/>
+      <family val="3"/>
       <charset val="129"/>
     </font>
   </fonts>
@@ -177,35 +216,38 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -215,7 +257,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -563,7 +605,7 @@
     <col min="5" max="5" width="38" customWidth="1"/>
     <col min="6" max="6" width="50.375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="36.875" customWidth="1"/>
-    <col min="8" max="8" width="7.875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="29.625" bestFit="1" customWidth="1"/>
     <col min="9" max="10" width="36.75" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="62.625" customWidth="1"/>
     <col min="12" max="12" width="52" customWidth="1"/>
@@ -572,184 +614,215 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
-      <c r="H1" s="7"/>
-      <c r="I1" s="7"/>
-      <c r="J1" s="7"/>
-      <c r="K1" s="7"/>
-      <c r="L1" s="3"/>
-      <c r="M1" s="3"/>
-      <c r="O1" s="3"/>
+      <c r="C1" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="6"/>
+      <c r="G1" s="6"/>
+      <c r="H1" s="6"/>
+      <c r="I1" s="6"/>
+      <c r="J1" s="6"/>
+      <c r="K1" s="6"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
+      <c r="O1" s="2"/>
     </row>
     <row r="2" spans="1:15">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" s="9"/>
-      <c r="E2" s="2"/>
-      <c r="L2" s="8"/>
-      <c r="M2" s="8"/>
-      <c r="O2" s="4"/>
+        <v>2</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H2" t="s">
+        <v>7</v>
+      </c>
+      <c r="L2" s="7"/>
+      <c r="M2" s="7"/>
+      <c r="O2" s="3"/>
     </row>
     <row r="3" spans="1:15">
-      <c r="H3" s="4"/>
-      <c r="M3" s="8"/>
-      <c r="N3" s="8"/>
+      <c r="F3" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H3" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="M3" s="7"/>
+      <c r="N3" s="7"/>
     </row>
     <row r="4" spans="1:15">
-      <c r="M4" s="8"/>
-      <c r="N4" s="8"/>
-      <c r="O4" s="4"/>
+      <c r="F4" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="G4" t="s">
+        <v>8</v>
+      </c>
+      <c r="H4" t="s">
+        <v>10</v>
+      </c>
+      <c r="M4" s="7"/>
+      <c r="N4" s="7"/>
+      <c r="O4" s="3"/>
     </row>
     <row r="5" spans="1:15">
-      <c r="L5" s="8"/>
-      <c r="M5" s="8"/>
-      <c r="O5" s="4"/>
+      <c r="L5" s="7"/>
+      <c r="M5" s="7"/>
+      <c r="O5" s="3"/>
     </row>
     <row r="6" spans="1:15">
-      <c r="L6" s="8"/>
-      <c r="M6" s="8"/>
-      <c r="O6" s="4"/>
+      <c r="L6" s="7"/>
+      <c r="M6" s="7"/>
+      <c r="O6" s="3"/>
     </row>
     <row r="7" spans="1:15">
-      <c r="L7" s="8"/>
-      <c r="M7" s="8"/>
-      <c r="O7" s="4"/>
+      <c r="L7" s="7"/>
+      <c r="M7" s="7"/>
+      <c r="O7" s="3"/>
     </row>
     <row r="8" spans="1:15">
-      <c r="L8" s="8"/>
-      <c r="M8" s="8"/>
-      <c r="O8" s="4"/>
+      <c r="L8" s="7"/>
+      <c r="M8" s="7"/>
+      <c r="O8" s="3"/>
     </row>
     <row r="9" spans="1:15">
-      <c r="L9" s="8"/>
-      <c r="M9" s="8"/>
-      <c r="O9" s="4"/>
+      <c r="L9" s="7"/>
+      <c r="M9" s="7"/>
+      <c r="O9" s="3"/>
     </row>
     <row r="10" spans="1:15">
-      <c r="D10" s="9"/>
-      <c r="L10" s="8"/>
-      <c r="M10" s="8"/>
-      <c r="O10" s="4"/>
+      <c r="D10" s="8"/>
+      <c r="L10" s="7"/>
+      <c r="M10" s="7"/>
+      <c r="O10" s="3"/>
     </row>
     <row r="11" spans="1:15">
-      <c r="D11" s="9"/>
-      <c r="L11" s="8"/>
-      <c r="M11" s="8"/>
-      <c r="O11" s="4"/>
+      <c r="D11" s="8"/>
+      <c r="L11" s="7"/>
+      <c r="M11" s="7"/>
+      <c r="O11" s="3"/>
     </row>
     <row r="12" spans="1:15">
-      <c r="D12" s="9"/>
-      <c r="L12" s="8"/>
-      <c r="M12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="L12" s="7"/>
+      <c r="M12" s="7"/>
     </row>
     <row r="13" spans="1:15">
-      <c r="D13" s="9"/>
-      <c r="L13" s="8"/>
-      <c r="M13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="L13" s="7"/>
+      <c r="M13" s="7"/>
     </row>
     <row r="14" spans="1:15">
-      <c r="D14" s="5"/>
+      <c r="D14" s="4"/>
       <c r="E14" s="1"/>
-      <c r="L14" s="8"/>
-      <c r="M14" s="8"/>
+      <c r="L14" s="7"/>
+      <c r="M14" s="7"/>
     </row>
     <row r="15" spans="1:15">
-      <c r="L15" s="8"/>
-      <c r="M15" s="8"/>
+      <c r="L15" s="7"/>
+      <c r="M15" s="7"/>
     </row>
     <row r="16" spans="1:15">
-      <c r="L16" s="8"/>
-      <c r="M16" s="8"/>
+      <c r="L16" s="7"/>
+      <c r="M16" s="7"/>
     </row>
     <row r="17" spans="4:13">
-      <c r="L17" s="8"/>
-      <c r="M17" s="8"/>
+      <c r="L17" s="7"/>
+      <c r="M17" s="7"/>
     </row>
     <row r="18" spans="4:13">
-      <c r="L18" s="8"/>
-      <c r="M18" s="8"/>
+      <c r="L18" s="7"/>
+      <c r="M18" s="7"/>
     </row>
     <row r="19" spans="4:13">
-      <c r="D19" s="9"/>
-      <c r="L19" s="8"/>
-      <c r="M19" s="8"/>
+      <c r="D19" s="8"/>
+      <c r="L19" s="7"/>
+      <c r="M19" s="7"/>
     </row>
     <row r="20" spans="4:13">
-      <c r="D20" s="6"/>
-      <c r="E20" s="10"/>
-      <c r="G20" s="4"/>
-      <c r="L20" s="8"/>
-      <c r="M20" s="8"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="9"/>
+      <c r="G20" s="3"/>
+      <c r="L20" s="7"/>
+      <c r="M20" s="7"/>
     </row>
     <row r="21" spans="4:13">
-      <c r="D21" s="6"/>
-      <c r="E21" s="10"/>
-      <c r="L21" s="8"/>
-      <c r="M21" s="8"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="9"/>
+      <c r="L21" s="7"/>
+      <c r="M21" s="7"/>
     </row>
     <row r="22" spans="4:13">
-      <c r="D22" s="6"/>
-      <c r="E22" s="10"/>
-      <c r="G22" s="6"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="9"/>
+      <c r="G22" s="5"/>
     </row>
     <row r="23" spans="4:13">
-      <c r="D23" s="6"/>
-      <c r="E23" s="10"/>
+      <c r="D23" s="5"/>
+      <c r="E23" s="9"/>
     </row>
     <row r="25" spans="4:13">
-      <c r="E25" s="10"/>
+      <c r="E25" s="9"/>
     </row>
     <row r="26" spans="4:13">
-      <c r="E26" s="10"/>
+      <c r="E26" s="9"/>
     </row>
     <row r="27" spans="4:13">
-      <c r="E27" s="10"/>
+      <c r="E27" s="9"/>
     </row>
     <row r="28" spans="4:13">
-      <c r="E28" s="10"/>
+      <c r="E28" s="9"/>
     </row>
     <row r="33" spans="5:7">
-      <c r="G33" s="6"/>
+      <c r="G33" s="5"/>
     </row>
     <row r="34" spans="5:7">
-      <c r="G34" s="11"/>
+      <c r="G34" s="10"/>
     </row>
     <row r="35" spans="5:7">
-      <c r="G35" s="6"/>
+      <c r="G35" s="5"/>
     </row>
     <row r="36" spans="5:7">
-      <c r="G36" s="6"/>
+      <c r="G36" s="5"/>
     </row>
     <row r="44" spans="5:7">
-      <c r="E44" s="12"/>
+      <c r="E44" s="11"/>
     </row>
     <row r="56" spans="7:7">
-      <c r="G56" s="13"/>
+      <c r="G56" s="12"/>
     </row>
     <row r="58" spans="7:7">
-      <c r="G58" s="13"/>
+      <c r="G58" s="12"/>
     </row>
     <row r="68" spans="7:7">
-      <c r="G68" s="6"/>
+      <c r="G68" s="5"/>
     </row>
     <row r="72" spans="7:7">
-      <c r="G72" s="6"/>
+      <c r="G72" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/resource/table/ko_narration_sets.xlsx
+++ b/resource/table/ko_narration_sets.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\work\LVPD_Studio\resource\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{180D5946-2295-46CD-A76C-019AF7807BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1554401A-306C-4079-9FCE-19BA97439D34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-27195" yWindow="14130" windowWidth="32745" windowHeight="15285" xr2:uid="{4ABACD07-DE77-46EA-95A9-D7C0914B6AEB}"/>
+    <workbookView xWindow="-29250" yWindow="7320" windowWidth="32745" windowHeight="12480" xr2:uid="{4ABACD07-DE77-46EA-95A9-D7C0914B6AEB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="16">
   <si>
     <t>id</t>
   </si>
@@ -79,6 +79,14 @@
   </si>
   <si>
     <t>ko-KR-HyunsuMultilingualNeural</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>과일 주문하기</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>과일 흥정하기</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -663,6 +671,18 @@
       <c r="O2" s="3"/>
     </row>
     <row r="3" spans="1:15">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="13" t="s">
+        <v>12</v>
+      </c>
       <c r="F3" s="13" t="s">
         <v>11</v>
       </c>
@@ -676,6 +696,18 @@
       <c r="N3" s="7"/>
     </row>
     <row r="4" spans="1:15">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" s="13" t="s">
+        <v>12</v>
+      </c>
       <c r="F4" s="13" t="s">
         <v>13</v>
       </c>

--- a/resource/table/ko_narration_sets.xlsx
+++ b/resource/table/ko_narration_sets.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\work\LVPD_Studio\resource\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1554401A-306C-4079-9FCE-19BA97439D34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD303CA5-1457-4393-A1B8-3178B5C558FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-29250" yWindow="7320" windowWidth="32745" windowHeight="12480" xr2:uid="{4ABACD07-DE77-46EA-95A9-D7C0914B6AEB}"/>
+    <workbookView xWindow="13155" yWindow="5505" windowWidth="32745" windowHeight="12480" xr2:uid="{4ABACD07-DE77-46EA-95A9-D7C0914B6AEB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="17">
   <si>
     <t>id</t>
   </si>
@@ -87,6 +87,10 @@
   </si>
   <si>
     <t>과일 흥정하기</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>헤이티 몇층</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -722,6 +726,18 @@
       <c r="O4" s="3"/>
     </row>
     <row r="5" spans="1:15">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D5" s="13" t="s">
+        <v>12</v>
+      </c>
       <c r="L5" s="7"/>
       <c r="M5" s="7"/>
       <c r="O5" s="3"/>

--- a/resource/table/ko_narration_sets.xlsx
+++ b/resource/table/ko_narration_sets.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\work\LVPD_Studio\resource\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD303CA5-1457-4393-A1B8-3178B5C558FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01CC254B-5C90-464C-96A8-616DA3534454}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13155" yWindow="5505" windowWidth="32745" windowHeight="12480" xr2:uid="{4ABACD07-DE77-46EA-95A9-D7C0914B6AEB}"/>
+    <workbookView xWindow="2340" yWindow="2340" windowWidth="32745" windowHeight="12480" xr2:uid="{4ABACD07-DE77-46EA-95A9-D7C0914B6AEB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="18">
   <si>
     <t>id</t>
   </si>
@@ -91,6 +91,10 @@
   </si>
   <si>
     <t>헤이티 몇층</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>바오패밀리</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -758,6 +762,18 @@
       <c r="O8" s="3"/>
     </row>
     <row r="9" spans="1:15">
+      <c r="A9">
+        <v>1000</v>
+      </c>
+      <c r="B9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D9" s="13" t="s">
+        <v>12</v>
+      </c>
       <c r="L9" s="7"/>
       <c r="M9" s="7"/>
       <c r="O9" s="3"/>

--- a/resource/table/ko_narration_sets.xlsx
+++ b/resource/table/ko_narration_sets.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\work\LVPD_Studio\resource\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01CC254B-5C90-464C-96A8-616DA3534454}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{210CE897-3F5F-4959-8C3A-10BB748E9D41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="2340" windowWidth="32745" windowHeight="12480" xr2:uid="{4ABACD07-DE77-46EA-95A9-D7C0914B6AEB}"/>
+    <workbookView xWindow="-34020" yWindow="5415" windowWidth="32745" windowHeight="12480" xr2:uid="{4ABACD07-DE77-46EA-95A9-D7C0914B6AEB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="19">
   <si>
     <t>id</t>
   </si>
@@ -95,6 +95,10 @@
   </si>
   <si>
     <t>바오패밀리</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>한시</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -779,7 +783,18 @@
       <c r="O9" s="3"/>
     </row>
     <row r="10" spans="1:15">
-      <c r="D10" s="8"/>
+      <c r="A10">
+        <v>1001</v>
+      </c>
+      <c r="B10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D10" s="13" t="s">
+        <v>12</v>
+      </c>
       <c r="L10" s="7"/>
       <c r="M10" s="7"/>
       <c r="O10" s="3"/>

--- a/resource/table/ko_narration_sets.xlsx
+++ b/resource/table/ko_narration_sets.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\work\LVPD_Studio\resource\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{210CE897-3F5F-4959-8C3A-10BB748E9D41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FE012F8-B9B3-45B1-80AB-C902ED552335}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-34020" yWindow="5415" windowWidth="32745" windowHeight="12480" xr2:uid="{4ABACD07-DE77-46EA-95A9-D7C0914B6AEB}"/>
+    <workbookView xWindow="-31305" yWindow="2490" windowWidth="32745" windowHeight="17535" xr2:uid="{4ABACD07-DE77-46EA-95A9-D7C0914B6AEB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="21">
   <si>
     <t>id</t>
   </si>
@@ -99,6 +99,14 @@
   </si>
   <si>
     <t>한시</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>hair-물온도</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>hair-스타일</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -751,11 +759,35 @@
       <c r="O5" s="3"/>
     </row>
     <row r="6" spans="1:15">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" s="13" t="s">
+        <v>12</v>
+      </c>
       <c r="L6" s="7"/>
       <c r="M6" s="7"/>
       <c r="O6" s="3"/>
     </row>
     <row r="7" spans="1:15">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D7" s="13" t="s">
+        <v>12</v>
+      </c>
       <c r="L7" s="7"/>
       <c r="M7" s="7"/>
       <c r="O7" s="3"/>

--- a/resource/table/ko_narration_sets.xlsx
+++ b/resource/table/ko_narration_sets.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\work\LVPD_Studio\resource\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FE012F8-B9B3-45B1-80AB-C902ED552335}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06072C87-26FF-43FC-A2D9-D5BBF08B0D02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-31305" yWindow="2490" windowWidth="32745" windowHeight="17535" xr2:uid="{4ABACD07-DE77-46EA-95A9-D7C0914B6AEB}"/>
+    <workbookView xWindow="-29550" yWindow="3915" windowWidth="32745" windowHeight="17535" xr2:uid="{4ABACD07-DE77-46EA-95A9-D7C0914B6AEB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="22">
   <si>
     <t>id</t>
   </si>
@@ -107,6 +107,10 @@
   </si>
   <si>
     <t>hair-스타일</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>한시-이순신</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -798,41 +802,16 @@
       <c r="O8" s="3"/>
     </row>
     <row r="9" spans="1:15">
-      <c r="A9">
-        <v>1000</v>
-      </c>
-      <c r="B9" t="s">
-        <v>17</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="D9" s="13" t="s">
-        <v>12</v>
-      </c>
       <c r="L9" s="7"/>
       <c r="M9" s="7"/>
       <c r="O9" s="3"/>
     </row>
     <row r="10" spans="1:15">
-      <c r="A10">
-        <v>1001</v>
-      </c>
-      <c r="B10" t="s">
-        <v>18</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="D10" s="13" t="s">
-        <v>12</v>
-      </c>
       <c r="L10" s="7"/>
       <c r="M10" s="7"/>
       <c r="O10" s="3"/>
     </row>
     <row r="11" spans="1:15">
-      <c r="D11" s="8"/>
       <c r="L11" s="7"/>
       <c r="M11" s="7"/>
       <c r="O11" s="3"/>
@@ -861,51 +840,86 @@
       <c r="L16" s="7"/>
       <c r="M16" s="7"/>
     </row>
-    <row r="17" spans="4:13">
+    <row r="17" spans="1:13">
+      <c r="A17">
+        <v>1000</v>
+      </c>
+      <c r="B17" t="s">
+        <v>17</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D17" s="13" t="s">
+        <v>12</v>
+      </c>
       <c r="L17" s="7"/>
       <c r="M17" s="7"/>
     </row>
-    <row r="18" spans="4:13">
+    <row r="18" spans="1:13">
+      <c r="A18">
+        <v>1001</v>
+      </c>
+      <c r="B18" t="s">
+        <v>18</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D18" s="13" t="s">
+        <v>12</v>
+      </c>
       <c r="L18" s="7"/>
       <c r="M18" s="7"/>
     </row>
-    <row r="19" spans="4:13">
-      <c r="D19" s="8"/>
+    <row r="19" spans="1:13">
+      <c r="A19">
+        <v>1002</v>
+      </c>
+      <c r="B19" t="s">
+        <v>21</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D19" s="13" t="s">
+        <v>11</v>
+      </c>
       <c r="L19" s="7"/>
       <c r="M19" s="7"/>
     </row>
-    <row r="20" spans="4:13">
+    <row r="20" spans="1:13">
       <c r="D20" s="5"/>
       <c r="E20" s="9"/>
       <c r="G20" s="3"/>
       <c r="L20" s="7"/>
       <c r="M20" s="7"/>
     </row>
-    <row r="21" spans="4:13">
+    <row r="21" spans="1:13">
       <c r="D21" s="5"/>
       <c r="E21" s="9"/>
       <c r="L21" s="7"/>
       <c r="M21" s="7"/>
     </row>
-    <row r="22" spans="4:13">
+    <row r="22" spans="1:13">
       <c r="D22" s="5"/>
       <c r="E22" s="9"/>
       <c r="G22" s="5"/>
     </row>
-    <row r="23" spans="4:13">
+    <row r="23" spans="1:13">
       <c r="D23" s="5"/>
       <c r="E23" s="9"/>
     </row>
-    <row r="25" spans="4:13">
+    <row r="25" spans="1:13">
       <c r="E25" s="9"/>
     </row>
-    <row r="26" spans="4:13">
+    <row r="26" spans="1:13">
       <c r="E26" s="9"/>
     </row>
-    <row r="27" spans="4:13">
+    <row r="27" spans="1:13">
       <c r="E27" s="9"/>
     </row>
-    <row r="28" spans="4:13">
+    <row r="28" spans="1:13">
       <c r="E28" s="9"/>
     </row>
     <row r="33" spans="5:7">

--- a/resource/table/ko_narration_sets.xlsx
+++ b/resource/table/ko_narration_sets.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\work\LVPD_Studio\resource\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06072C87-26FF-43FC-A2D9-D5BBF08B0D02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE92C67F-F571-4F8C-91B1-BC4AEFBF3B60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-29550" yWindow="3915" windowWidth="32745" windowHeight="17535" xr2:uid="{4ABACD07-DE77-46EA-95A9-D7C0914B6AEB}"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{4ABACD07-DE77-46EA-95A9-D7C0914B6AEB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="25">
   <si>
     <t>id</t>
   </si>
@@ -111,6 +111,18 @@
   </si>
   <si>
     <t>한시-이순신</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>고수</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>찬물</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>결제</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -797,16 +809,52 @@
       <c r="O7" s="3"/>
     </row>
     <row r="8" spans="1:15">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D8" s="13" t="s">
+        <v>12</v>
+      </c>
       <c r="L8" s="7"/>
       <c r="M8" s="7"/>
       <c r="O8" s="3"/>
     </row>
     <row r="9" spans="1:15">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D9" s="13" t="s">
+        <v>12</v>
+      </c>
       <c r="L9" s="7"/>
       <c r="M9" s="7"/>
       <c r="O9" s="3"/>
     </row>
     <row r="10" spans="1:15">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D10" s="13" t="s">
+        <v>12</v>
+      </c>
       <c r="L10" s="7"/>
       <c r="M10" s="7"/>
       <c r="O10" s="3"/>
